--- a/docs/static/data/webretriever_results.xlsx
+++ b/docs/static/data/webretriever_results.xlsx
@@ -86,7 +86,7 @@
     <t>https://arxiv.org/abs/2407.13032</t>
   </si>
   <si>
-    <t>Emergence AI,24</t>
+    <t>Emergence AI, 24</t>
   </si>
   <si>
     <t>UI-TARS</t>
@@ -143,7 +143,7 @@
     <t>https://www.anthropic.com/news/claude-sonnet-4-5</t>
   </si>
   <si>
-    <t>Anthropic, '25</t>
+    <t>Anthropic, 25</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1374,7 @@
     <col min="3" max="3" width="12.6666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="45.7777777777778" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.5555555555556" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.86111111111111" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.2222222222222" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.6666666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.3333333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.2222222222222" style="1" customWidth="1"/>
@@ -1593,7 +1593,7 @@
         <v>35.2</v>
       </c>
       <c r="K6" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
@@ -1671,7 +1671,7 @@
         <v>40.1</v>
       </c>
       <c r="K8" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
